--- a/astro-site/public/dl/plan-negocio-food-truck/checklist-apertura-food-truck.xlsx
+++ b/astro-site/public/dl/plan-negocio-food-truck/checklist-apertura-food-truck.xlsx
@@ -14,7 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5 - Marketing" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6 - 90 Dias" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1 - Constitucion'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'F2 - Vehiculo'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'F3 - Equipamiento'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'F4 - Personal'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'F5 - Marketing'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6 - 90 Dias'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +58,11 @@
     <font>
       <name val="Calibri"/>
       <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -91,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,10 +118,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -469,9 +492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -495,6 +518,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -763,13 +787,53 @@
         <is>
           <t>A todo riesgo recomendado</t>
         </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(A5:A13,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(B5:B13,"?*")</f>
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -777,7 +841,813 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — FOOD TRUCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FASE 2: VEHICULO Y PERMISOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TRAMITE / ACCION</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PLAZO</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NOTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Seleccion y compra vehiculo</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2-6 semanas</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Furgoneta adaptada, remolque o trailer. Nuevo o 2a mano</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Adaptacion vehiculo para cocina</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Taller especializado</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>4-8 semanas</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Ventanilla, mostrador, instalaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Certificacion gas (si cocina a gas)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Instalador autorizado</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Revision anual obligatoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>ITV especial (si modificacion estructural)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ITV</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1 dia</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Obligatorio si se modifica carroceria</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Proyecto tecnico sanitario</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Ingeniero</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2-3 semanas</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Planos instalacion, flujos, depositos agua</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Autorizacion sanitaria vehiculo</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Sanidad CCAA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2-4 semanas</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Inspeccion del vehiculo equipado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Permiso venta ambulante (municipal)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Ayuntamiento</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>1-3 meses</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>CADA municipio tiene su normativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Permiso ocupacion via publica</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Ayuntamiento</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1-2 meses</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Si operas en espacio publico fijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Inscripcion en mercados/ferias</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Organizadores</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Muchos mercados tienen lista de espera</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Carnet conducir adecuado</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>B para &lt;3.500kg, C para mayor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(A5:A14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:E14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — FOOD TRUCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FASE 3: EQUIPAMIENTO Y SETUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TRAMITE / ACCION</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PLAZO</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NOTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Plancha industrial (gas o electrica)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>1-2 semanas</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Adaptar al concepto: burgers, crepes, plancha...</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Freidora (si aplica)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Con filtro y gestion aceite usado</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Campana extractora con filtros</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>1-2 semanas</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Obligatoria en espacio cerrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Nevera/congelador compacto</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>12V o 220V segun generador</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Generador electrico insonorizado</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>5-7 kW minimo, insonorizado (&lt;70dB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Deposito agua limpia + residual</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Minimo 40L limpia + 60L residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Fregadero doble seno</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Con adaptacion</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Obligatorio por normativa sanitaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>TPV movil + datafono 4G</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Tablet + datafono, cobertura 4G</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Menaje y utensilios cocina</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Adaptado al espacio reducido</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Packaging biodegradable</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Obligatorio en muchos municipios desde 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Rotulacion integral vehiculo</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Rotulista</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>1-2 semanas</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Primera impresion, marca visible a distancia</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Toldo, mesas plegables, banderolas</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Kit montaje rapido para cada servicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C18">
+        <f>COUNTIF(A5:A16,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E18">
+        <f>COUNTIF(B5:B16,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:E16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -799,10 +1669,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 2: VEHICULO Y PERMISOS</t>
-        </is>
-      </c>
-    </row>
+          <t>FASE 4: PERSONAL Y FORMACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -838,7 +1709,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Seleccion y compra vehiculo</t>
+          <t>Definir equipo minimo (2-3 personas)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -848,12 +1719,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>2-6 semanas</t>
+          <t>1 semana</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Furgoneta adaptada, remolque o trailer. Nuevo o 2a mano</t>
+          <t>Propietario + 1 ayudante minimo</t>
         </is>
       </c>
     </row>
@@ -865,22 +1736,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Adaptacion vehiculo para cocina</t>
+          <t>Contratacion ayudante (si aplica)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Taller especializado</t>
+          <t>Gestor</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>4-8 semanas</t>
+          <t>1-2 semanas</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Ventanilla, mostrador, instalaciones</t>
+          <t>Contrato temporal o fijo-discontinuo para eventos</t>
         </is>
       </c>
     </row>
@@ -892,22 +1763,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Certificacion gas (si cocina a gas)</t>
+          <t>Carnet manipulador alimentos</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Instalador autorizado</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Revision anual obligatoria</t>
+          <t>Obligatorio todo personal</t>
         </is>
       </c>
     </row>
@@ -919,12 +1790,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ITV especial (si modificacion estructural)</t>
+          <t>Formacion APPCC movil</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ITV</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -934,7 +1805,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Obligatorio si se modifica carroceria</t>
+          <t>Temperaturas, cadena frio en vehiculo, trazabilidad</t>
         </is>
       </c>
     </row>
@@ -946,22 +1817,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Proyecto tecnico sanitario</t>
+          <t>Formacion operativa food truck</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Ingeniero</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>2-3 semanas</t>
+          <t>1 semana</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Planos instalacion, flujos, depositos agua</t>
+          <t>Setup, servicio rapido, teardown, limpieza</t>
         </is>
       </c>
     </row>
@@ -973,22 +1844,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Autorizacion sanitaria vehiculo</t>
+          <t>Plan PRL (prevencion riesgos)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Sanidad CCAA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2-4 semanas</t>
+          <t>1-2 semanas</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Inspeccion del vehiculo equipado</t>
+          <t>Riesgos especificos: gas, aceite, espacio reducido</t>
         </is>
       </c>
     </row>
@@ -1000,22 +1871,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Permiso venta ambulante (municipal)</t>
+          <t>Protocolo alergenos</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Ayuntamiento</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1-3 meses</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>CADA municipio tiene su normativa</t>
+          <t>14 alergenos, cartel visible en food truck</t>
         </is>
       </c>
     </row>
@@ -1027,92 +1898,78 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Permiso ocupacion via publica</t>
+          <t>Ensayo montaje/desmontaje completo</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Ayuntamiento</t>
+          <t>Equipo</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1-2 meses</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Si operas en espacio publico fijo</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Inscripcion en mercados/ferias</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Organizadores</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Muchos mercados tienen lista de espera</t>
-        </is>
-      </c>
-    </row>
+          <t>Cronometrar: objetivo &lt;30 min montaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Carnet conducir adecuado</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>B para &lt;3.500kg, C para mayor</t>
-        </is>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>COUNTIF(A5:A12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E14">
+        <f>COUNTIF(B5:B12,"?*")</f>
+        <v>8.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1134,10 +1991,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 3: EQUIPAMIENTO Y SETUP</t>
-        </is>
-      </c>
-    </row>
+          <t>FASE 5: MARKETING Y LANZAMIENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1173,22 +2031,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Plancha industrial (gas o electrica)</t>
+          <t>Crear identidad visual y marca</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Disenador</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>1-2 semanas</t>
+          <t>2-3 semanas</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Adaptar al concepto: burgers, crepes, plancha...</t>
+          <t>Logo, colores, rotulacion, packaging branded</t>
         </is>
       </c>
     </row>
@@ -1200,22 +2058,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Freidora (si aplica)</t>
+          <t>Ficha Google My Business</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Con filtro y gestion aceite usado</t>
+          <t>Categoria: Food truck. Fotos, ubicaciones</t>
         </is>
       </c>
     </row>
@@ -1227,22 +2085,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Campana extractora con filtros</t>
+          <t>Perfiles RRSS (Instagram + TikTok)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Instalador</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1-2 semanas</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Obligatoria en espacio cerrado</t>
+          <t>Video del truck + comida = viral potencial</t>
         </is>
       </c>
     </row>
@@ -1254,22 +2112,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Nevera/congelador compacto</t>
+          <t>Pagina web con calendario ubicaciones</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Dev</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>1-2 semanas</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>12V o 220V segun generador</t>
+          <t>Donde estaras cada dia de la semana</t>
         </is>
       </c>
     </row>
@@ -1281,22 +2139,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Generador electrico insonorizado</t>
+          <t>Sesion fotos/video profesional</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Fotografo</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>5-7 kW minimo, insonorizado (&lt;70dB)</t>
+          <t>Comida en accion, truck rotulado, servicio</t>
         </is>
       </c>
     </row>
@@ -1308,22 +2166,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Deposito agua limpia + residual</t>
+          <t>Acuerdos con mercados y eventos</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Instalador</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>2-4 semanas</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Minimo 40L limpia + 60L residual</t>
+          <t>Mercados fijos semanales = ingresos recurrentes</t>
         </is>
       </c>
     </row>
@@ -1335,22 +2193,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Fregadero doble seno</t>
+          <t>Registro en apps de food trucks</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Instalador</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Con adaptacion</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Obligatorio por normativa sanitaria</t>
+          <t>Roaming Hunger, apps locales de street food</t>
         </is>
       </c>
     </row>
@@ -1362,22 +2220,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>TPV movil + datafono 4G</t>
+          <t>Acuerdos con empresas/oficinas</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>2 semanas</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Tablet + datafono, cobertura 4G</t>
+          <t>Lunch corporativo: recurrencia garantizada</t>
         </is>
       </c>
     </row>
@@ -1389,22 +2247,22 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Menaje y utensilios cocina</t>
+          <t>Evento de inauguracion</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>1 dia</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Adaptado al espacio reducido</t>
+          <t>Primer servicio con promo: 2x1, redes, influencers</t>
         </is>
       </c>
     </row>
@@ -1416,12 +2274,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Packaging biodegradable</t>
+          <t>Programa fidelizacion movil</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1431,79 +2289,65 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Obligatorio en muchos municipios desde 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Rotulacion integral vehiculo</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Rotulista</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>1-2 semanas</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Primera impresion, marca visible a distancia</t>
-        </is>
-      </c>
-    </row>
+          <t>Tarjeta digital o QR: 10o menu gratis</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Toldo, mesas plegables, banderolas</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>1 semana</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Kit montaje rapido para cada servicio</t>
-        </is>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(A5:A14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1523,10 +2367,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 4: PERSONAL Y FORMACION</t>
-        </is>
-      </c>
-    </row>
+          <t>FASE 6: PRIMEROS 90 DIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1562,7 +2407,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Definir equipo minimo (2-3 personas)</t>
+          <t>Testear ubicaciones (minimo 5)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1572,12 +2417,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>Mes 1</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Propietario + 1 ayudante minimo</t>
+          <t>Evaluar facturacion por ubicacion y dia</t>
         </is>
       </c>
     </row>
@@ -1589,22 +2434,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Contratacion ayudante (si aplica)</t>
+          <t>Registro diario ventas por ubicacion</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Gestor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1-2 semanas</t>
+          <t>Diario</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Contrato temporal o fijo-discontinuo para eventos</t>
+          <t>Saber que ubicaciones funcionan y cuales no</t>
         </is>
       </c>
     </row>
@@ -1616,22 +2461,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Carnet manipulador alimentos</t>
+          <t>Control food cost semanal</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>Semanal</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Obligatorio todo personal</t>
+          <t>Pesar genero, controlar mermas, ajustar pedidos</t>
         </is>
       </c>
     </row>
@@ -1643,7 +2488,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Formacion APPCC movil</t>
+          <t>Ajustar carta segun ventas</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -1653,12 +2498,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>Mes 1</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Temperaturas, cadena frio en vehiculo, trazabilidad</t>
+          <t>Eliminar platos lentos, potenciar bestsellers</t>
         </is>
       </c>
     </row>
@@ -1670,7 +2515,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Formacion operativa food truck</t>
+          <t>Optimizar ruta semanal</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1680,12 +2525,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1 semana</t>
+          <t>Mes 1-2</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Setup, servicio rapido, teardown, limpieza</t>
+          <t>Fijar los mejores dias/ubicaciones como ruta fija</t>
         </is>
       </c>
     </row>
@@ -1697,22 +2542,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Plan PRL (prevencion riesgos)</t>
+          <t>Encuestas clientes + resenas Google</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1-2 semanas</t>
+          <t>Mes 1-3</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Riesgos especificos: gas, aceite, espacio reducido</t>
+          <t>Pedir resenas, responder todas</t>
         </is>
       </c>
     </row>
@@ -1724,7 +2569,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Protocolo alergenos</t>
+          <t>Evaluar eventos y festivales</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1734,12 +2579,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>Mes 2</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>14 alergenos, cartel visible en food truck</t>
+          <t>Festivales = facturacion x3-5 en un dia</t>
         </is>
       </c>
     </row>
@@ -1751,699 +2596,123 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Ensayo montaje/desmontaje completo</t>
+          <t>Renegociar proveedores</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Equipo</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>Mes 2</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Cronometrar: objetivo &lt;30 min montaje</t>
-        </is>
+          <t>Con volumen real, pedir mejores precios</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Primer cierre trimestral</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Comparar P&amp;L real vs plan financiero</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Plan expansion (2o truck o local)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Si funciona, evaluar segundo vehiculo o local fijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(A5:A14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — FOOD TRUCK</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FASE 5: MARKETING Y LANZAMIENTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TRAMITE / ACCION</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PLAZO</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>NOTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Crear identidad visual y marca</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Disenador</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2-3 semanas</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Logo, colores, rotulacion, packaging branded</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Ficha Google My Business</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Categoria: Food truck. Fotos, ubicaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Perfiles RRSS (Instagram + TikTok)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Video del truck + comida = viral potencial</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Pagina web con calendario ubicaciones</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>1-2 semanas</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Donde estaras cada dia de la semana</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Sesion fotos/video profesional</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Fotografo</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Comida en accion, truck rotulado, servicio</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Acuerdos con mercados y eventos</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>2-4 semanas</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Mercados fijos semanales = ingresos recurrentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Registro en apps de food trucks</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Roaming Hunger, apps locales de street food</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Acuerdos con empresas/oficinas</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>2 semanas</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Lunch corporativo: recurrencia garantizada</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Evento de inauguracion</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>1 dia</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Primer servicio con promo: 2x1, redes, influencers</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Programa fidelizacion movil</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>1 semana</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Tarjeta digital o QR: 10o menu gratis</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — FOOD TRUCK</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FASE 6: PRIMEROS 90 DIAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TRAMITE / ACCION</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PLAZO</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>NOTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Testear ubicaciones (minimo 5)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Mes 1</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Evaluar facturacion por ubicacion y dia</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Registro diario ventas por ubicacion</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Diario</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Saber que ubicaciones funcionan y cuales no</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Control food cost semanal</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Semanal</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Pesar genero, controlar mermas, ajustar pedidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Ajustar carta segun ventas</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Mes 1</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Eliminar platos lentos, potenciar bestsellers</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Optimizar ruta semanal</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Mes 1-2</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Fijar los mejores dias/ubicaciones como ruta fija</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Encuestas clientes + resenas Google</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Mes 1-3</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Pedir resenas, responder todas</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Evaluar eventos y festivales</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Mes 2</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Festivales = facturacion x3-5 en un dia</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Renegociar proveedores</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Mes 2</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Con volumen real, pedir mejores precios</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Primer cierre trimestral</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Gestor</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Mes 3</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Comparar P&amp;L real vs plan financiero</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Plan expansion (2o truck o local)</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Mes 3</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Si funciona, evaluar segundo vehiculo o local fijo</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/plan-negocio-food-truck/checklist-apertura-food-truck.xlsx
+++ b/astro-site/public/dl/plan-negocio-food-truck/checklist-apertura-food-truck.xlsx
@@ -7,20 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F1 - Constitucion" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F2 - Vehiculo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F1 - Constitución" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F2 - Vehículo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F3 - Equipamiento" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F4 - Personal" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5 - Marketing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6 - 90 Dias" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6 - 90 Días" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1 - Constitucion'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'F2 - Vehiculo'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1 - Constitución'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'F2 - Vehículo'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'F3 - Equipamiento'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'F4 - Personal'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'F5 - Marketing'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6 - 90 Dias'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6 - 90 Días'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +66,13 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +89,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F5F0E8"/>
         <bgColor rgb="00F5F0E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,16 +130,47 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00C8E6C9"/>
           <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -494,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -514,7 +556,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 1: CONSTITUCION Y TRAMITES</t>
+          <t>FASE 1: CONSTITUCIÓN Y TRÁMITES</t>
         </is>
       </c>
     </row>
@@ -527,7 +569,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -547,14 +589,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Elegir forma juridica (SL o autonomo)</t>
+          <t>Elegir forma jurídica (SL o autónomo)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -569,19 +611,19 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Autonomo viable si empiezas solo, SL si hay socios</t>
+          <t>Autónomo viable si empiezas solo, SL si hay socios</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Constitucion SL / alta autonomo</t>
+          <t>Constitución SL / alta autónomo</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -591,17 +633,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1-5 dias</t>
+          <t>1-5 días</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Capital 1 EUR Ley Crea y Crece</t>
+          <t>Capital 1 € Ley Crea y Crece</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -618,17 +660,17 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Epigrafe IAE: 671.4 o 677.9 (venta ambulante)</t>
+          <t>Epígrafe IAE: 672.x (servicios de restauración en quioscos, food trucks e instalaciones móviles análogas) o 677.9 (venta ambulante sin elaboración) — la elección la valida tu gestor según si elaboras el producto en el vehículo o sólo lo vendes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -645,17 +687,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Tarifa plana autonomos 80 EUR/mes</t>
+          <t>Cuota según la base mínima del tramo que te corresponda. Consulta el importe del ejercicio en curso y verifica con tu gestoría si te aplica la cuota reducida de inicio de actividad</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -672,17 +714,17 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1-3 dias</t>
+          <t>1-3 días</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Imprescindible tramites telematicos</t>
+          <t>Imprescindible para los trámites telemáticos</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -699,7 +741,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1-3 dias</t>
+          <t>1-3 días</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -709,19 +751,19 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Registro sanitario RGSEAA</t>
+          <t>Inscripción en el Registro Sanitario de tu Comunidad Autónoma (declaración responsable de inicio de actividad alimentaria)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Sanidad</t>
+          <t>Sanidad CCAA</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -731,12 +773,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Obligatorio para elaboracion alimentaria</t>
+          <t>El Registro General Sanitario estatal NO aplica al minorista que sirve al consumidor final (art. 2.2 del RD 191/2011): el que te toca es el autonómico, el mismo que pide la fase 2 de este checklist con la autorización sanitaria del vehículo</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -753,24 +795,24 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Minimo 300.000 EUR, cubre intoxicaciones</t>
+          <t>Mínimo 300.000 €, cubre intoxicaciones</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Seguro vehiculo (furgoneta/remolque)</t>
+          <t>Seguro del vehículo (furgoneta o remolque)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -780,7 +822,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -789,38 +831,98 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Registro de actividades de tratamiento de datos personales</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Art. 30 del RGPD y art. 31 de la LOPDGDD: lo pide la AEPD en la primera inspección. Incluye clientes del programa de fidelización, personal y proveedores</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="105" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Adaptar el TPV móvil al sistema Veri*factu / factura electrónica</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>El RD 1007/2023 y su calendario escalonado obligan a que el software de facturación sea verificable. Consulta la fecha que te aplica antes de comprar el TPV móvil y el datáfono que ya presupuesta la hoja de Inversión Inicial: cambiarlo después cuesta el doble</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C15">
-        <f>COUNTIF(A5:A13,"✓")</f>
+      <c r="C17" s="13">
+        <f>COUNTIF(A5:A15,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E15">
-        <f>COUNTIF(B5:B13,"?*")</f>
-        <v>9.0</v>
+      <c r="E17" s="13">
+        <f>COUNTIF(B5:B15,"?*")-COUNTIF(A5:A15,"N/A")</f>
+        <v>11.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E13">
+  <conditionalFormatting sqref="A5:E15">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A15">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -843,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -863,7 +965,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 2: VEHICULO Y PERMISOS</t>
+          <t>FASE 2: VEHÍCULO Y PERMISOS</t>
         </is>
       </c>
     </row>
@@ -876,7 +978,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -896,14 +998,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Seleccion y compra vehiculo</t>
+          <t>Selección y compra del vehículo</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -923,14 +1025,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Adaptacion vehiculo para cocina</t>
+          <t>Adaptación del vehículo para cocina</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -950,14 +1052,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Certificacion gas (si cocina a gas)</t>
+          <t>Certificación gas (si cocina a gas)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -972,19 +1074,19 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Revision anual obligatoria</t>
+          <t>Revisión anual obligatoria</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ITV especial (si modificacion estructural)</t>
+          <t>ITV especial (si modificación estructural)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -994,24 +1096,24 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Obligatorio si se modifica carroceria</t>
+          <t>Obligatorio si se modifica la carrocería</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Proyecto tecnico sanitario</t>
+          <t>Proyecto técnico sanitario</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1026,19 +1128,19 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Planos instalacion, flujos, depositos agua</t>
+          <t>Planos de instalación, flujos y depósitos de agua</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Autorizacion sanitaria vehiculo</t>
+          <t>Autorización sanitaria del vehículo</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1053,12 +1155,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Inspeccion del vehiculo equipado</t>
+          <t>Inspección del vehículo ya equipado</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1085,14 +1187,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Permiso ocupacion via publica</t>
+          <t>Permiso de ocupación de la vía pública</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1107,19 +1209,19 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Si operas en espacio publico fijo</t>
+          <t>Si operas en espacio público fijo</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Inscripcion en mercados/ferias</t>
+          <t>Inscripción en mercados/ferias</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1139,7 +1241,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1165,38 +1267,125 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="8" t="inlineStr">
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Hojas de reclamaciones oficiales y su cartel anunciador</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>1 día</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>También son obligatorias en venta ambulante: el modelo y el texto del cartel los aprueba tu Comunidad Autónoma</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="75" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Contrato con gestor autorizado de residuos y aceite usado</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Se comprueba en la inspección sanitaria del vehículo. Este mismo checklist ya avisa de que la freidora genera aceite usado que hay que gestionar, pero nunca contrataba el servicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Contrato de desinsectación, desratización y desinfección (DDD)</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Empresa inscrita en el ROESB; el certificado forma parte del plan APPCC móvil que ya exige la fase 4 de este checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C16">
-        <f>COUNTIF(A5:A14,"✓")</f>
+      <c r="C19" s="13">
+        <f>COUNTIF(A5:A17,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E16">
-        <f>COUNTIF(B5:B14,"?*")</f>
-        <v>10.0</v>
+      <c r="E19" s="13">
+        <f>COUNTIF(B5:B17,"?*")-COUNTIF(A5:A17,"N/A")</f>
+        <v>13.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E14">
+  <conditionalFormatting sqref="A5:E17">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A17">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1252,7 +1441,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1272,14 +1461,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Plancha industrial (gas o electrica)</t>
+          <t>Plancha industrial (gas o eléctrica)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1299,7 +1488,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1321,12 +1510,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Con filtro y gestion aceite usado</t>
+          <t>Con filtro y gestión aceite usado</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1353,7 +1542,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1375,19 +1564,19 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>12V o 220V segun generador</t>
+          <t>12V o 220V según generador</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Generador electrico insonorizado</t>
+          <t>Generador eléctrico insonorizado</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1402,19 +1591,19 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>5-7 kW minimo, insonorizado (&lt;70dB)</t>
+          <t>5-7 kW mínimo, insonorizado (&lt;70dB)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Deposito agua limpia + residual</t>
+          <t>Depósito de agua limpia y de aguas residuales</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1429,12 +1618,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Minimo 40L limpia + 60L residual</t>
+          <t>Mínimo 40 L de agua limpia y 60 L de residual</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1451,7 +1640,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Con adaptacion</t>
+          <t>Con adaptación</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1461,14 +1650,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>TPV movil + datafono 4G</t>
+          <t>TPV móvil y datáfono 4G</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1483,12 +1672,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Tablet + datafono, cobertura 4G</t>
+          <t>Tablet y datáfono con cobertura 4G</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1515,7 +1704,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1542,14 +1731,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Rotulacion integral vehiculo</t>
+          <t>Rotulación integral del vehículo</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1564,12 +1753,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Primera impresion, marca visible a distancia</t>
+          <t>Primera impresión, marca visible a distancia</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1591,7 +1780,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Kit montaje rapido para cada servicio</t>
+          <t>Kit de montaje rápido para cada servicio</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1791,7 @@
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C18">
+      <c r="C18" s="13">
         <f>COUNTIF(A5:A16,"✓")</f>
         <v>0.0</v>
       </c>
@@ -1611,12 +1800,13 @@
           <t>de</t>
         </is>
       </c>
-      <c r="E18">
-        <f>COUNTIF(B5:B16,"?*")</f>
+      <c r="E18" s="13">
+        <f>COUNTIF(B5:B16,"?*")-COUNTIF(A5:A16,"N/A")</f>
         <v>12.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -1625,8 +1815,13 @@
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A16">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1649,7 +1844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1864,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 4: PERSONAL Y FORMACION</t>
+          <t>FASE 4: PERSONAL Y FORMACIÓN</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1877,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1702,14 +1897,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Definir equipo minimo (2-3 personas)</t>
+          <t>Definir equipo mínimo (2-3 personas)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1724,19 +1919,19 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Propietario + 1 ayudante minimo</t>
+          <t>Propietario + 1 ayudante mínimo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Contratacion ayudante (si aplica)</t>
+          <t>Contratación ayudante (si aplica)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1756,41 +1951,41 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Carnet manipulador alimentos</t>
+          <t>Formación en higiene alimentaria de todo el equipo</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Obligatorio todo personal</t>
+          <t>El «carnet de manipulador» está derogado (RD 109/2010): la formación la acredita la EMPRESA y se documenta en el plan APPCC móvil</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Formacion APPCC movil</t>
+          <t>Formación en APPCC móvil</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -1800,24 +1995,24 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Temperaturas, cadena frio en vehiculo, trazabilidad</t>
+          <t>Temperaturas, cadena de frío en el vehículo y trazabilidad</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Formacion operativa food truck</t>
+          <t>Formación operativa food truck</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1832,24 +2027,24 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Setup, servicio rapido, teardown, limpieza</t>
+          <t>Montaje, servicio rápido, desmontaje y limpieza</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Plan PRL (prevencion riesgos)</t>
+          <t>Plan PRL (prevención riesgos)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>Titular o servicio ajeno</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1859,19 +2054,19 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Riesgos especificos: gas, aceite, espacio reducido</t>
+          <t>Riesgos específicos: gas, aceite, espacio reducido</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Protocolo alergenos</t>
+          <t>Protocolo alérgenos</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1881,17 +2076,17 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>14 alergenos, cartel visible en food truck</t>
+          <t>14 alérgenos, cartel visible en food truck</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1908,7 +2103,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1917,38 +2112,98 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="8" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Registro horario diario de la jornada de todo el equipo</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Desde el primer contrato</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Art. 34.9 del Estatuto de los Trabajadores; se conserva cuatro años. Aplica desde el primer contrato del ayudante, aunque sea a tiempo parcial</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Informar al equipo del registro horario y del tratamiento de sus datos</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Desde el primer contrato</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>La cláusula informativa se entrega con el contrato; el fichaje es un tratamiento de datos, no sólo una obligación laboral</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C14">
-        <f>COUNTIF(A5:A12,"✓")</f>
+      <c r="C16" s="13">
+        <f>COUNTIF(A5:A14,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E14">
-        <f>COUNTIF(B5:B12,"?*")</f>
-        <v>8.0</v>
+      <c r="E16" s="13">
+        <f>COUNTIF(B5:B14,"?*")-COUNTIF(A5:A14,"N/A")</f>
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E12">
+  <conditionalFormatting sqref="A5:E14">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A14">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1971,7 +2226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2004,7 +2259,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2024,7 +2279,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2036,7 +2291,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Disenador</t>
+          <t>Diseñador</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -2046,12 +2301,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Logo, colores, rotulacion, packaging branded</t>
+          <t>Logo, colores, rotulación, packaging branded</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2068,17 +2323,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Categoria: Food truck. Fotos, ubicaciones</t>
+          <t>Categoría: Food truck. Fotos, ubicaciones</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2095,7 +2350,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2105,14 +2360,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Pagina web con calendario ubicaciones</t>
+          <t>Página web con el calendario de ubicaciones</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -2127,39 +2382,39 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Donde estaras cada dia de la semana</t>
+          <t>Dónde estarás cada día de la semana</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Sesion fotos/video profesional</t>
+          <t>Sesión fotos/video profesional</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Fotografo</t>
+          <t>Fotógrafo</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Comida en accion, truck rotulado, servicio</t>
+          <t>Comida en acción, truck rotulado, servicio</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2186,7 +2441,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2203,7 +2458,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -2213,7 +2468,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2240,14 +2495,14 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Evento de inauguracion</t>
+          <t>Evento de inauguración</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2257,7 +2512,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1 dia</t>
+          <t>1 día</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2267,14 +2522,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Programa fidelizacion movil</t>
+          <t>Programa de fidelización móvil</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2289,42 +2544,102 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Tarjeta digital o QR: 10o menu gratis</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="8" t="inlineStr">
+          <t>Tarjeta digital o QR: el décimo menú, gratis</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Licencia de derechos de autor por música ambiental en ferias y festivales (SGAE/AGEDI-AIE)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Antes de poner música propia</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Distinta de la licencia del organizador del festival, que cubre el recinto, no cada puesto individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Cláusula informativa y consentimiento en el programa de fidelización con QR</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>El propio checklist promete un programa de fidelización móvil con QR que recoge datos de contacto: necesita su información previa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C16">
-        <f>COUNTIF(A5:A14,"✓")</f>
+      <c r="C18" s="13">
+        <f>COUNTIF(A5:A16,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E16">
-        <f>COUNTIF(B5:B14,"?*")</f>
-        <v>10.0</v>
+      <c r="E18" s="13">
+        <f>COUNTIF(B5:B16,"?*")-COUNTIF(A5:A16,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E14">
+  <conditionalFormatting sqref="A5:E16">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A16">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2367,7 +2682,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 6: PRIMEROS 90 DIAS</t>
+          <t>FASE 6: PRIMEROS 90 DÍAS</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2695,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE / ACCION</t>
+          <t>TRÁMITE / ACCIÓN</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2400,14 +2715,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Testear ubicaciones (minimo 5)</t>
+          <t>Testear ubicaciones (mínimo 5)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2422,19 +2737,19 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Evaluar facturacion por ubicacion y dia</t>
+          <t>Evaluar facturación por ubicación y día</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Registro diario ventas por ubicacion</t>
+          <t>Registro diario ventas por ubicación</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -2449,12 +2764,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Saber que ubicaciones funcionan y cuales no</t>
+          <t>Saber qué ubicaciones funcionan y cuáles no</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2476,19 +2791,19 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Pesar genero, controlar mermas, ajustar pedidos</t>
+          <t>Pesar el género, controlar mermas y ajustar pedidos</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Ajustar carta segun ventas</t>
+          <t>Ajustar carta según ventas</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -2508,7 +2823,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2530,19 +2845,19 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Fijar los mejores dias/ubicaciones como ruta fija</t>
+          <t>Fijar los mejores días/ubicaciones como ruta fija</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Encuestas clientes + resenas Google</t>
+          <t>Encuestas a clientes y reseñas de Google</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -2557,12 +2872,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Pedir resenas, responder todas</t>
+          <t>Pedir reseñas, responder todas</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2584,12 +2899,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Festivales = facturacion x3-5 en un dia</t>
+          <t>Festivales = facturación x3-5 en un día</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2616,7 +2931,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2643,14 +2958,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Plan expansion (2o truck o local)</t>
+          <t>Plan de expansión (segundo truck o local fijo)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2665,7 +2980,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Si funciona, evaluar segundo vehiculo o local fijo</t>
+          <t>Si funciona, evaluar un segundo vehículo o un local fijo</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2991,7 @@
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C16">
+      <c r="C16" s="13">
         <f>COUNTIF(A5:A14,"✓")</f>
         <v>0.0</v>
       </c>
@@ -2685,12 +3000,13 @@
           <t>de</t>
         </is>
       </c>
-      <c r="E16">
-        <f>COUNTIF(B5:B14,"?*")</f>
+      <c r="E16" s="13">
+        <f>COUNTIF(B5:B14,"?*")-COUNTIF(A5:A14,"N/A")</f>
         <v>10.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -2699,8 +3015,13 @@
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A14">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2715,4 +3036,96 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>INSTRUCCIONES DE USO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Este fichero forma parte del producto «plan-negocio-food-truck» de AI Chef Pro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Las celdas VERDES son las editables: cambia esas y el resto del libro se recalcula solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Columna OK: elige ✓ (hecho), ☐ (pendiente) o N/A (no aplica). Las N/A no cuentan en el total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>El contador de cada pestaña cuenta sólo las ✓; las N/A salen del total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Para editar una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Más plantillas y kits del catálogo en aichef.pro/productos-digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Versión 2.2 · septiembre 2026 · aichef.pro/plan-negocio-food-truck · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
 </file>